--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.48845943353758</v>
+        <v>3.979374657949857</v>
       </c>
       <c r="D2" t="n">
-        <v>23.04984945643968</v>
+        <v>3.745600536671448</v>
       </c>
       <c r="E2" t="n">
-        <v>6.149799621276555</v>
+        <v>0.9993424384574401</v>
       </c>
       <c r="F2" t="n">
-        <v>5.884418776269886</v>
+        <v>0.9562180511438565</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.78805867609069</v>
+        <v>5.978059534864737</v>
       </c>
       <c r="D3" t="n">
-        <v>34.81868700897945</v>
+        <v>5.658036638959161</v>
       </c>
       <c r="E3" t="n">
-        <v>6.149799621276555</v>
+        <v>0.9993424384574401</v>
       </c>
       <c r="F3" t="n">
-        <v>5.884418776269886</v>
+        <v>0.9562180511438565</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
